--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/자동추정_지출목록.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/자동추정_지출목록.xlsx
@@ -1690,7 +1690,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -1714,7 +1713,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -1738,7 +1736,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -1762,7 +1759,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -1786,7 +1782,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -1810,7 +1805,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -1834,7 +1828,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -1858,7 +1851,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -1882,7 +1874,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -1906,7 +1897,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -1930,7 +1920,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -1954,7 +1943,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -1978,7 +1966,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -2002,7 +1989,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -2026,7 +2012,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -2050,7 +2035,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -2074,7 +2058,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -2098,7 +2081,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -2122,7 +2104,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -2146,7 +2127,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -2170,7 +2150,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -2194,7 +2173,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -2218,7 +2196,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -2242,7 +2219,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -2266,7 +2242,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -2290,7 +2265,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -2314,7 +2288,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -2338,7 +2311,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -2362,7 +2334,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -2386,7 +2357,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -2410,7 +2380,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -2434,7 +2403,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -2458,7 +2426,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -2482,7 +2449,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -2506,7 +2472,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -2530,7 +2495,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -2554,7 +2518,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -2578,7 +2541,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -2602,7 +2564,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -2626,7 +2587,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -2650,7 +2610,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -2674,7 +2633,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -2698,7 +2656,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -2722,7 +2679,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -2746,7 +2702,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -2770,7 +2725,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -2794,7 +2748,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -2818,7 +2771,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -2842,7 +2794,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -2866,7 +2817,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -2890,7 +2840,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -2914,7 +2863,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -2938,7 +2886,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -2962,7 +2909,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -2986,7 +2932,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -3010,7 +2955,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -3034,7 +2978,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -3058,7 +3001,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -3082,7 +3024,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -3106,7 +3047,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -3130,7 +3070,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -3154,7 +3093,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -3178,7 +3116,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -3202,7 +3139,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -3226,7 +3162,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -3250,7 +3185,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -3274,7 +3208,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -3298,7 +3231,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -3322,7 +3254,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -3346,7 +3277,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -3370,7 +3300,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -3394,7 +3323,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -3418,7 +3346,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -3442,7 +3369,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -3466,7 +3392,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -3490,7 +3415,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -3514,7 +3438,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -3538,7 +3461,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -3562,7 +3484,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -3586,7 +3507,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -3610,7 +3530,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -3634,7 +3553,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -3658,7 +3576,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -3682,7 +3599,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -3706,7 +3622,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -3730,7 +3645,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -3754,7 +3668,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -3778,7 +3691,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -3802,7 +3714,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -3826,7 +3737,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -3850,7 +3760,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -3874,7 +3783,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -3898,7 +3806,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -3922,7 +3829,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -3946,7 +3852,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -3970,7 +3875,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -3994,7 +3898,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -4018,7 +3921,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -4042,7 +3944,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -4066,7 +3967,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -4090,7 +3990,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -4114,7 +4013,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -4138,7 +4036,6 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -4162,9 +4059,13 @@
           <t>반영</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="'반영' 또는 '제외'만 입력할 수 있습니다." type="list">
+      <formula1>"반영,제외"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/자동추정_지출목록.xlsx
+++ b/01-Projects/에이팜건강-주간자금계획-자동화/자금계획_자동화/04_기준파일/자동추정_지출목록.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="안내" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="자동추정" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="별칭" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -928,7 +929,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>반영</t>
+          <t>제외</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>취합파일 농협카드 6,827,883원과 중복 (9월)</t>
         </is>
       </c>
     </row>
@@ -4068,4 +4074,51 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>정기지출명</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>별칭(쉼표로 여러 개)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>같은 달에 취합 지출예정 파일에 별칭과 비슷한 항목이 있으면 해당 자동추정은 금액과 무관하게 제외됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NH기업카드</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>농협카드</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>